--- a/coretp/plans/sdtrig_icount/Sdtrig_Icount_TP.xlsx
+++ b/coretp/plans/sdtrig_icount/Sdtrig_Icount_TP.xlsx
@@ -2,21 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
-  <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
+  <workbookPr hidePivotFieldList="true" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njoaquin/Documents/Human Readable Testplan/GENERATED/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78CDFDE-A12E-6B4F-97F4-9112332967BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34560" yWindow="-13720" windowWidth="51200" windowHeight="27200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34560" yWindow="-13720" windowWidth="51200" windowHeight="27200"/>
   </bookViews>
   <sheets>
     <sheet name="Sdtrig-Icount" sheetId="14" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sdtrig-Icount'!$A$1:$F$21</definedName>
+    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'Sdtrig-Icount'!$A$1:$F$21</definedName>
     <definedName name="Actual">(PeriodInActual*(#REF!&gt;0))*PeriodInPlan</definedName>
     <definedName name="ActualBeyond">PeriodInActual*(#REF!&gt;0)</definedName>
     <definedName name="PercentComplete">PercentCompleteBeyond*PeriodInPlan</definedName>
@@ -48,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="108">
   <si>
     <t>Scenario ID</t>
   </si>
@@ -296,10 +295,10 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="12"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">priv_mode = pick_any {M, S, VS}
@@ -312,10 +311,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
-        <color rgb="FFAEAAAA"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <color rgb="FFAEAAAA"/>
+        <sz val="12"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">- Single‑step is enabled via DM (dcsr.step = 1).
@@ -323,10 +322,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="12"/>
         <scheme val="minor"/>
       </rPr>
       <t>- A pending interrupt (e.g. timer) exists when I executes.</t>
@@ -697,172 +696,238 @@
 AssertException(cause=ExceptionCause.BREAKPOINT, skip_pc_check=True, code=[ConfigureIcountTrigger(index=8, count=1, action=TriggerAction.BREAKPOINT, priv_mode=("m",)), MemAccess(memory=mem, op="lr.w")])
 AssertException(cause=ExceptionCause.BREAKPOINT, skip_pc_check=True, code=[ConfigureIcountTrigger(index=8, count=1, action=TriggerAction.BREAKPOINT, priv_mode=("m",)), MemAccess(memory=mem, op="cbo.clean")])</t>
   </si>
+  <si>
+    <t>Comment(comment="icount tdata1.count WARL: count=0 no fire, count=1 fires, max-value fires after max retires")
+count = 0 -&gt; must not fire
+ConfigureIcountTrigger(index=8, count=0, action=TriggerAction.BREAKPOINT)
+Directive(directive="nop")
+count = 1 -&gt; fires on the next instruction
+AssertException(cause=ExceptionCause.BREAKPOINT, skip_pc_check=True, code=[ConfigureIcountTrigger(index=8, count=1, action=TriggerAction.BREAKPOINT), Directive(directive="nop")])
+count = 16 -&gt; fires on the 17th matching instruction, so the block carries 16 nops to keep the
+fire inside it. A shorter block puts the fire in the assertion's failure trampoline, and the
+re-executed instruction then falls through to the failure jump.
+AssertException(cause=ExceptionCause.BREAKPOINT, skip_pc_check=True, code=[ConfigureIcountTrigger(index=8, count=16, action=TriggerAction.BREAKPOINT), *[Directive(directive="nop") for _ in range(16)]])
+count = 0x3FFF (max of the 14-bit field). A fire needs 16384 matching retires, far more than any
+assertable block, so this case checks the other half of the WARL contract: the max count must be
+accepted and must not fire early. hit[24] clear after the filler proves it stayed armed without
+tripping.
+ConfigureIcountTrigger(index=8, count=0x3FFF, action=TriggerAction.BREAKPOINT)
+[Directive(directive="nop") for _ in range(16)]
+ReadTriggerCsr(csr_name="tdata1", direct_read=False)
+LoadImmediateStep(imm=(1 &lt;&lt; 24))
+Arithmetic(op="and", src1=rd_cmax, src2=hit_mask)
+LoadImmediateStep(imm=0)
+AssertEqual(src1=cmax_hit, src2=zero)
+ConfigureIcountTrigger(index=8, count=0, action=TriggerAction.BREAKPOINT, priv_mode=())</t>
+  </si>
+  <si>
+    <t>Comment(comment="icount interaction with WFI under various wake sources")
+SelectTrigger(index=8)
+AssertException(cause=ExceptionCause.BREAKPOINT, skip_pc_check=True, code=[ConfigureIcountTrigger(index=8, count=1, action=TriggerAction.BREAKPOINT, priv_mode=("m",)), Directive(directive="wfi")])
+LoadImmediateStep(imm=(1&lt;&lt;3))
+CsrWrite(csr_name="mip", set_mask=msip_bit, direct_write=True)
+AssertException(cause=ExceptionCause.BREAKPOINT, skip_pc_check=True, code=[ConfigureIcountTrigger(index=8, count=1, action=TriggerAction.BREAKPOINT, priv_mode=("m",)), Directive(directive="wfi")])
+wfi + wrs sequence. Both wait ops live inside the block so the count=2 countdown runs out on
+them rather than in the assertion's failure path.
+AssertException(cause=ExceptionCause.BREAKPOINT, skip_pc_check=True, code=[ConfigureIcountTrigger(index=8, count=2, action=TriggerAction.BREAKPOINT, priv_mode=("m",)), Directive(directive="wrs.nto"), Directive(directive="wfi")])</t>
+  </si>
+  <si>
+    <t>priv_mode = pick_all {M, S, U, HS, VS, VU}
+handler_type = pick_all {breakpoint, interrupt, non-breakpoint exception}
+The plan-wide setup clears medeleg, so breakpoints are handled in M-mode, where the post-handler
+can reach the trigger CSRs. The scenario therefore covers the M-handler path only; the delegated
+S and VS handler paths are not exercised here. Reaching them would need the plan-wide handler
+hook reworked to run in the delegated mode, since a scenario-local medeleg write is undone by
+that hook.</t>
+  </si>
+  <si>
+    <t>Comment(comment="icount does not re-fire while inside its own handler (no re-entrancy)")
+AssertException(cause=ExceptionCause.BREAKPOINT, skip_pc_check=True, code=[ConfigureIcountTrigger(index=8, count=1, action=TriggerAction.BREAKPOINT, priv_mode=("m",)), LoadImmediateStep(imm=(1&lt;&lt;3))])
+AssertException(cause=ExceptionCause.BREAKPOINT, skip_pc_check=True, expected_handler_mode=ExceptionHandlerMode.MACHINE, re_execute=False, code=[ConfigureIcountTrigger(index=8, count=1, action=TriggerAction.BREAKPOINT, priv_mode=("m",)), Directive(directive="nop")])</t>
+  </si>
+  <si>
+    <t>Comment(comment="icount is precise even under multi-instruction retirement; fires after exactly K instrs")
+Each block carries K nops so the count=K countdown runs out inside the assertion. The trigger
+fires on the (K+1)-th matching instruction, and a block shorter than that puts the fire in the
+assertion's own failure trampoline, where re-execution then falls through to the failure jump.
+For each K in {1, 2, 3}:
+AssertException(cause=ExceptionCause.BREAKPOINT, skip_pc_check=True, code=[ConfigureIcountTrigger(index=8, count=K, action=TriggerAction.BREAKPOINT), *[Directive(directive="nop") for _ in range(K)]])</t>
+  </si>
+  <si>
+    <t>Comment(comment="icount must not count flushed speculative instructions past a mispredicted branch")
+The branch sequence lives inside AssertException.code so the count=4 countdown is consumed by
+these instructions. Only br and tgt retire -- the two speculative nops sit on the flushed path --
+so the fire lands on the trailing nops, which is the property under test. Padding to count
+matching instructions matters: the trigger fires on the (count+1)-th one, and if the block is
+shorter the fire lands in the assertion's own failure trampoline and re-execution walks into it.
+AssertException(cause=ExceptionCause.BREAKPOINT, skip_pc_check=True, code=[ConfigureIcountTrigger(index=8, count=4, action=TriggerAction.BREAKPOINT), Directive(directive="beq x0, x0, 1f"), Directive(directive="nop"), Directive(directive="nop"), Directive(directive="1: nop"), Directive(directive="nop"), Directive(directive="nop")])</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <fonts count="23">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1" tint="0.24994659260841701"/>
       <name val="Calibri Light"/>
       <family val="2"/>
+      <color theme="1" tint="0.249946592608417"/>
+      <sz val="11"/>
       <scheme val="major"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="7"/>
       <name val="Calibri Light"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="7"/>
+      <sz val="13"/>
       <scheme val="major"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="1" tint="0.24994659260841701"/>
       <name val="Calibri Light"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1" tint="0.249946592608417"/>
+      <sz val="13"/>
       <scheme val="major"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1" tint="0.34998626667073579"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1" tint="0.3499862666707358"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="1" tint="0.24994659260841701"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1" tint="0.249946592608417"/>
+      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1" tint="0.24994659260841701"/>
       <name val="Calibri Light"/>
       <family val="2"/>
+      <color theme="1" tint="0.249946592608417"/>
+      <sz val="12"/>
       <scheme val="major"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1" tint="0.24994659260841701"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1" tint="0.249946592608417"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="7"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <i val="1"/>
+      <color theme="7"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="42"/>
-      <color theme="7"/>
       <name val="Calibri Light"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="7"/>
+      <sz val="42"/>
       <scheme val="major"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="2" tint="-0.499984740745262"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="2" tint="-0.499984740745262"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="2" tint="-0.499984740745262"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="2" tint="-0.499984740745262"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FFAEAAAA"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FFAEAAAA"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="2" tint="-0.499984740745262"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="2" tint="-0.499984740745262"/>
+      <sz val="12"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -882,19 +947,19 @@
     <fill>
       <patternFill patternType="lightUp">
         <fgColor theme="7"/>
-        <bgColor theme="9" tint="0.59996337778862885"/>
+        <bgColor theme="9" tint="0.5999633777886288"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor auto="1"/>
+        <bgColor auto="true"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="lightUp">
         <fgColor theme="7"/>
-        <bgColor theme="7" tint="0.59996337778862885"/>
+        <bgColor theme="7" tint="0.5999633777886288"/>
       </patternFill>
     </fill>
     <fill>
@@ -904,7 +969,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59996337778862885"/>
+        <fgColor theme="9" tint="0.5999633777886288"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -916,7 +981,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -972,34 +1037,34 @@
       <left/>
       <right/>
       <top style="thin">
-        <color theme="9" tint="-0.24994659260841701"/>
+        <color theme="9" tint="-0.249946592608417"/>
       </top>
       <bottom style="thin">
-        <color theme="9" tint="-0.24994659260841701"/>
+        <color theme="9" tint="-0.249946592608417"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1133,181 +1198,181 @@
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyProtection="false">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFill="false" applyBorder="false" applyProtection="false">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyFill="false" applyBorder="false" applyProtection="false">
+      <alignment horizontal="left" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFill="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFill="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyFill="0" applyProtection="0">
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyFill="false" applyProtection="false">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFill="0" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFill="false" applyProtection="false">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFill="false" applyBorder="false" applyProtection="false">
+      <alignment horizontal="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFill="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFill="false" applyProtection="false">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyProtection="false">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyNumberFormat="false" applyFont="false" applyAlignment="false">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyNumberFormat="false" applyFont="false" applyAlignment="false">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" applyNumberFormat="false" applyFont="false" applyAlignment="false">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" applyNumberFormat="false" applyFont="false" applyAlignment="false">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" applyNumberFormat="false" applyFont="false" applyAlignment="false">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="6" fillId="7" borderId="4">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" applyNumberFormat="false" applyProtection="false">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="9" xfId="0" applyFont="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="15" xfId="0" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="20">
-    <cellStyle name="% complete" xfId="12" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="% complete (beyond plan) legend" xfId="10" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="Activity" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Actual (beyond plan) legend" xfId="11" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Actual legend" xfId="13" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Explanatory Text 2" xfId="17" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="Heading 1 2" xfId="18" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Heading 2 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Heading 3 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
-    <cellStyle name="Heading 4 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="Label" xfId="9" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="% complete" xfId="12"/>
+    <cellStyle name="% complete (beyond plan) legend" xfId="10"/>
+    <cellStyle name="Activity" xfId="3"/>
+    <cellStyle name="Actual (beyond plan) legend" xfId="11"/>
+    <cellStyle name="Actual legend" xfId="13"/>
+    <cellStyle name="Explanatory Text 2" xfId="17"/>
+    <cellStyle name="Heading 1 2" xfId="18"/>
+    <cellStyle name="Heading 2 2" xfId="4"/>
+    <cellStyle name="Heading 3 2" xfId="6"/>
+    <cellStyle name="Heading 4 2" xfId="8"/>
+    <cellStyle name="Label" xfId="9"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
-    <cellStyle name="Percent Complete" xfId="2" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
-    <cellStyle name="Period Headers" xfId="5" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="Period Highlight Control" xfId="16" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
-    <cellStyle name="Period Value" xfId="15" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
-    <cellStyle name="Plan legend" xfId="14" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
-    <cellStyle name="Project Headers" xfId="7" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
-    <cellStyle name="Title 2" xfId="19" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Percent Complete" xfId="2"/>
+    <cellStyle name="Period Headers" xfId="5"/>
+    <cellStyle name="Period Highlight Control" xfId="16"/>
+    <cellStyle name="Period Value" xfId="15"/>
+    <cellStyle name="Plan legend" xfId="14"/>
+    <cellStyle name="Project Headers" xfId="7"/>
+    <cellStyle name="Title 2" xfId="19"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1320,7 +1385,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office 2013 - 2022 Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -1617,17 +1682,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B9BCED4-710A-47D2-9DCB-92251DAE159F}">
   <dimension ref="A1:XET125"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="71.1640625" customWidth="1"/>
-    <col min="5" max="5" width="72" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="6" max="6" width="255.83203125" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col bestFit="true" customWidth="true" max="1" min="1" width="15.5"/>
+    <col bestFit="true" customWidth="true" max="2" min="2" width="20"/>
+    <col bestFit="true" customWidth="true" max="3" min="3" style="2" width="24.6640625"/>
+    <col customWidth="true" max="4" min="4" width="71.1640625"/>
+    <col bestFit="true" customWidth="true" max="5" min="5" outlineLevel="1" width="72"/>
+    <col bestFit="true" customWidth="true" max="6" min="6" outlineLevel="1" width="255.83203125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6 16374:16374" s="11" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6 16374:16374" s="11" customFormat="true" ht="19">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1647,7 +1712,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:6 16374:16374" s="15" customFormat="1" ht="85" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6 16374:16374" s="15" customFormat="true" ht="85">
       <c r="A2" s="17" t="s">
         <v>8</v>
       </c>
@@ -1667,7 +1732,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="3" spans="1:6 16374:16374" s="23" customFormat="1" ht="221" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6 16374:16374" s="23" customFormat="true" ht="221">
       <c r="A3" s="20" t="s">
         <v>12</v>
       </c>
@@ -1687,7 +1752,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:6 16374:16374" s="23" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6 16374:16374" s="23" customFormat="true" ht="409.6">
       <c r="A4" s="20" t="s">
         <v>15</v>
       </c>
@@ -1707,7 +1772,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:6 16374:16374" s="23" customFormat="1" ht="255" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6 16374:16374" s="23" customFormat="true" ht="255">
       <c r="A5" s="20" t="s">
         <v>18</v>
       </c>
@@ -1727,7 +1792,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:6 16374:16374" s="23" customFormat="1" ht="187" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6 16374:16374" s="23" customFormat="true" ht="187">
       <c r="A6" s="20" t="s">
         <v>21</v>
       </c>
@@ -1747,7 +1812,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="1:6 16374:16374" s="23" customFormat="1" ht="102" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6 16374:16374" s="23" customFormat="true" ht="102">
       <c r="A7" s="20" t="s">
         <v>24</v>
       </c>
@@ -1764,10 +1829,10 @@
         <v>26</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
     </row>
-    <row r="8" spans="1:6 16374:16374" s="28" customFormat="1" ht="289" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6 16374:16374" s="28" customFormat="true" ht="289">
       <c r="A8" s="25" t="s">
         <v>27</v>
       </c>
@@ -1787,7 +1852,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:6 16374:16374" s="32" customFormat="1" ht="153" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6 16374:16374" s="32" customFormat="true" ht="153">
       <c r="A9" s="29" t="s">
         <v>30</v>
       </c>
@@ -1807,7 +1872,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:6 16374:16374" s="23" customFormat="1" ht="119" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6 16374:16374" s="23" customFormat="true" ht="119">
       <c r="A10" s="21" t="s">
         <v>34</v>
       </c>
@@ -1827,7 +1892,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="11" spans="1:6 16374:16374" s="23" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6 16374:16374" s="23" customFormat="true" ht="409.6">
       <c r="A11" s="21" t="s">
         <v>37</v>
       </c>
@@ -1847,7 +1912,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:6 16374:16374" s="35" customFormat="1" ht="204" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6 16374:16374" s="35" customFormat="true" ht="204">
       <c r="A12" s="21" t="s">
         <v>40</v>
       </c>
@@ -1867,7 +1932,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="13" spans="1:6 16374:16374" s="23" customFormat="1" ht="119" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6 16374:16374" s="23" customFormat="true" ht="119">
       <c r="A13" s="21" t="s">
         <v>43</v>
       </c>
@@ -1887,7 +1952,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="14" spans="1:6 16374:16374" s="35" customFormat="1" ht="187" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6 16374:16374" s="35" customFormat="true" ht="187">
       <c r="A14" s="21" t="s">
         <v>46</v>
       </c>
@@ -1907,7 +1972,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="15" spans="1:6 16374:16374" s="35" customFormat="1" ht="136" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6 16374:16374" s="35" customFormat="true" ht="136">
       <c r="A15" s="34" t="s">
         <v>50</v>
       </c>
@@ -1924,11 +1989,11 @@
         <v>52</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="XET15" s="23"/>
     </row>
-    <row r="16" spans="1:6 16374:16374" s="35" customFormat="1" ht="102" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6 16374:16374" s="35" customFormat="true" ht="102">
       <c r="A16" s="37" t="s">
         <v>53</v>
       </c>
@@ -1948,7 +2013,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="17" spans="1:16374" s="35" customFormat="1" ht="221" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16374" s="35" customFormat="true" ht="221">
       <c r="A17" s="37" t="s">
         <v>56</v>
       </c>
@@ -1968,7 +2033,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="18" spans="1:16374" s="23" customFormat="1" ht="187" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16374" s="23" customFormat="true" ht="187">
       <c r="A18" s="21" t="s">
         <v>59</v>
       </c>
@@ -1988,7 +2053,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="19" spans="1:16374" s="35" customFormat="1" ht="136" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16374" s="35" customFormat="true" ht="136">
       <c r="A19" s="37" t="s">
         <v>62</v>
       </c>
@@ -2002,13 +2067,13 @@
         <v>64</v>
       </c>
       <c r="E19" s="40" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="F19" s="42" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
-    <row r="20" spans="1:16374" s="23" customFormat="1" ht="136" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16374" s="23" customFormat="true" ht="136">
       <c r="A20" s="22" t="s">
         <v>66</v>
       </c>
@@ -2025,10 +2090,10 @@
         <v>69</v>
       </c>
       <c r="F20" s="33" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
-    <row r="21" spans="1:16374" s="35" customFormat="1" ht="102" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16374" s="35" customFormat="true" ht="102">
       <c r="A21" s="22" t="s">
         <v>70</v>
       </c>
@@ -2045,11 +2110,11 @@
         <v>72</v>
       </c>
       <c r="F21" s="24" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="XET21" s="23"/>
     </row>
-    <row r="22" spans="1:16374" s="23" customFormat="1" ht="136" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16374" s="23" customFormat="true" ht="136">
       <c r="A22" s="22" t="s">
         <v>73</v>
       </c>
@@ -2069,7 +2134,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="23" spans="1:16374" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16374" s="23" customFormat="true">
       <c r="A23" s="10"/>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
@@ -2077,7 +2142,7 @@
       <c r="E23" s="7"/>
       <c r="F23" s="10"/>
     </row>
-    <row r="24" spans="1:16374" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16374">
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
@@ -18446,8 +18511,63 @@
       <c r="XER24" s="6"/>
       <c r="XES24" s="6"/>
     </row>
-    <row r="48" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48" ht="16.5" customHeight="true"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81" spans="1:6">
       <c r="A81" s="12"/>
       <c r="B81" s="12"/>
       <c r="C81" s="12"/>
@@ -18455,11 +18575,52 @@
       <c r="E81" s="8"/>
       <c r="F81" s="12"/>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107" spans="1:4">
       <c r="A107" s="1"/>
       <c r="D107" s="1"/>
     </row>
-    <row r="124" spans="1:6" ht="64" x14ac:dyDescent="0.2">
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124" spans="1:6" ht="64">
       <c r="A124" s="3" t="s">
         <v>62</v>
       </c>
@@ -18475,9 +18636,9 @@
       <c r="E124" s="6"/>
       <c r="F124" s="6"/>
     </row>
-    <row r="125" spans="1:6" ht="114" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" spans="1:6" ht="114" customHeight="true"/>
   </sheetData>
-  <autoFilter ref="A1:F21" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F21"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
